--- a/processed_data/hard_data_exports/hunt_tables/2026/2026_ELK_BULL_ALL.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/2026_ELK_BULL_ALL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_elk_bull_all" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026_elk_bull_all" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026_elk_bull_all'!$A$3:$J$356</definedName>
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J356"/>
+  <dimension ref="A1:N356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -614,6 +614,26 @@
           <t>Total</t>
         </is>
       </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Prior Year</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Harvest Success (Prior Year %)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Average Harvest Age (Prior Year)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Average Days Hunted (Prior Year)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -654,6 +674,20 @@
       <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" s="6" t="inlineStr"/>
       <c r="J4" s="6" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -694,6 +728,20 @@
       <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -734,6 +782,20 @@
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -774,6 +836,20 @@
       <c r="H7" s="8" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -814,6 +890,20 @@
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
       <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -854,6 +944,20 @@
       <c r="H9" s="8" t="inlineStr"/>
       <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -898,6 +1002,20 @@
           <t>750</t>
         </is>
       </c>
+      <c r="K10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>42.2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="54" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -938,6 +1056,20 @@
       <c r="H11" s="8" t="inlineStr"/>
       <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>25.1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -978,6 +1110,20 @@
       <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" s="6" t="inlineStr"/>
       <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>14.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="54" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
@@ -1018,6 +1164,20 @@
       <c r="H13" s="8" t="inlineStr"/>
       <c r="I13" s="8" t="inlineStr"/>
       <c r="J13" s="8" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1062,6 +1222,20 @@
           <t>500</t>
         </is>
       </c>
+      <c r="K14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>55.1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
@@ -1114,6 +1288,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>76.9</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -1166,6 +1354,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
@@ -1218,6 +1420,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -1270,6 +1486,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
@@ -1322,6 +1552,20 @@
           <t>165</t>
         </is>
       </c>
+      <c r="K19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>30.4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>13.9</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -1374,6 +1618,20 @@
           <t>21</t>
         </is>
       </c>
+      <c r="K20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>31.8</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
@@ -1426,6 +1684,20 @@
           <t>40</t>
         </is>
       </c>
+      <c r="K21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>41.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
@@ -1478,6 +1750,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
@@ -1530,6 +1816,20 @@
           <t>21</t>
         </is>
       </c>
+      <c r="K23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
@@ -1582,6 +1882,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
@@ -1634,6 +1948,20 @@
           <t>19</t>
         </is>
       </c>
+      <c r="K25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -1686,6 +2014,20 @@
           <t>93</t>
         </is>
       </c>
+      <c r="K26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
@@ -1738,6 +2080,20 @@
           <t>32</t>
         </is>
       </c>
+      <c r="K27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -1790,6 +2146,20 @@
           <t>28</t>
         </is>
       </c>
+      <c r="K28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
@@ -1842,6 +2212,20 @@
           <t>145</t>
         </is>
       </c>
+      <c r="K29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -1894,6 +2278,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>90.9</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
@@ -1946,6 +2344,20 @@
           <t>17</t>
         </is>
       </c>
+      <c r="K31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
@@ -1998,6 +2410,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
@@ -2050,6 +2476,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -2102,6 +2542,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
@@ -2154,6 +2608,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K35" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -2206,6 +2674,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
@@ -2258,6 +2740,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K37" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -2310,6 +2806,20 @@
           <t>68</t>
         </is>
       </c>
+      <c r="K38" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>70.8</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
@@ -2362,6 +2872,20 @@
           <t>113</t>
         </is>
       </c>
+      <c r="K39" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>81.1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
@@ -2414,6 +2938,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K40" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>68.8</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
@@ -2466,6 +3004,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K41" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
@@ -2518,6 +3070,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K42" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
@@ -2570,6 +3136,20 @@
           <t>16</t>
         </is>
       </c>
+      <c r="K43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>47.1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -2622,6 +3202,20 @@
           <t>27</t>
         </is>
       </c>
+      <c r="K44" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
@@ -2674,6 +3268,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K45" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -2726,6 +3334,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K46" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
@@ -2778,6 +3400,20 @@
           <t>9</t>
         </is>
       </c>
+      <c r="K47" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="5" t="inlineStr">
@@ -2830,6 +3466,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K48" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
@@ -2882,6 +3532,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K49" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>90.9</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
@@ -2934,6 +3598,20 @@
           <t>8</t>
         </is>
       </c>
+      <c r="K50" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
@@ -2986,6 +3664,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>84.6</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
@@ -3038,6 +3730,20 @@
           <t>38</t>
         </is>
       </c>
+      <c r="K52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
@@ -3090,6 +3796,20 @@
           <t>110</t>
         </is>
       </c>
+      <c r="K53" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -3142,6 +3862,20 @@
           <t>63</t>
         </is>
       </c>
+      <c r="K54" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>84.4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
@@ -3194,6 +3928,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K55" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>78.9</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -3246,6 +3994,20 @@
           <t>22</t>
         </is>
       </c>
+      <c r="K56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
@@ -3298,6 +4060,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -3350,6 +4126,20 @@
           <t>33</t>
         </is>
       </c>
+      <c r="K58" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
@@ -3402,6 +4192,20 @@
           <t>60</t>
         </is>
       </c>
+      <c r="K59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>67.6</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -3454,6 +4258,20 @@
           <t>99</t>
         </is>
       </c>
+      <c r="K60" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
@@ -3506,6 +4324,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K61" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>92.9</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -3558,6 +4390,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K62" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
@@ -3610,6 +4456,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K63" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -3662,6 +4522,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K64" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
@@ -3714,6 +4588,20 @@
           <t>99</t>
         </is>
       </c>
+      <c r="K65" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>72.1</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -3766,6 +4654,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K66" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
@@ -3818,6 +4720,20 @@
           <t>24</t>
         </is>
       </c>
+      <c r="K67" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -3870,6 +4786,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K68" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
@@ -3922,6 +4852,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K69" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -3974,6 +4918,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K70" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
@@ -4026,6 +4984,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K71" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -4078,6 +5050,20 @@
           <t>56</t>
         </is>
       </c>
+      <c r="K72" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
@@ -4130,6 +5116,20 @@
           <t>19</t>
         </is>
       </c>
+      <c r="K73" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -4182,6 +5182,20 @@
           <t>17</t>
         </is>
       </c>
+      <c r="K74" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
@@ -4234,6 +5248,20 @@
           <t>87</t>
         </is>
       </c>
+      <c r="K75" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="48" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -4286,6 +5314,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K76" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="48" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
@@ -4338,6 +5380,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="48" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -4390,6 +5446,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K78" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
@@ -4442,6 +5512,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K79" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -4494,6 +5578,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K80" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>73.9</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="48" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
@@ -4546,6 +5644,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K81" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="48" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -4598,6 +5710,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K82" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="48" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
@@ -4650,6 +5776,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K83" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -4702,6 +5842,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K84" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="48" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
@@ -4754,6 +5908,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K85" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="48" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -4806,6 +5974,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K86" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="48" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
@@ -4858,6 +6040,20 @@
           <t>11</t>
         </is>
       </c>
+      <c r="K87" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>19.8</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="48" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -4910,6 +6106,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K88" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="48" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
@@ -4962,6 +6172,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K89" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="48" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -5014,6 +6238,20 @@
           <t>17</t>
         </is>
       </c>
+      <c r="K90" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>14.9</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
@@ -5066,6 +6304,20 @@
           <t>195</t>
         </is>
       </c>
+      <c r="K91" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>69.2</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="5" t="inlineStr">
@@ -5116,6 +6368,20 @@
       <c r="J92" s="6" t="inlineStr">
         <is>
           <t>172</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>68.7</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -5158,6 +6424,20 @@
       <c r="H93" s="8" t="inlineStr"/>
       <c r="I93" s="8" t="inlineStr"/>
       <c r="J93" s="8" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -5210,6 +6490,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K94" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
@@ -5262,6 +6556,20 @@
           <t>24</t>
         </is>
       </c>
+      <c r="K95" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
@@ -5314,6 +6622,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K96" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>22.2</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
@@ -5366,6 +6688,20 @@
           <t>23</t>
         </is>
       </c>
+      <c r="K97" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="5" t="inlineStr">
@@ -5418,6 +6754,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K98" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>10.9</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="32" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
@@ -5470,6 +6820,20 @@
           <t>24</t>
         </is>
       </c>
+      <c r="K99" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>59.3</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="32" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
@@ -5522,6 +6886,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K100" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>55.6</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="32" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
@@ -5574,6 +6952,20 @@
           <t>23</t>
         </is>
       </c>
+      <c r="K101" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="32" customHeight="1">
       <c r="A102" s="5" t="inlineStr">
@@ -5626,6 +7018,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K102" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
@@ -5678,6 +7084,20 @@
           <t>35</t>
         </is>
       </c>
+      <c r="K103" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
@@ -5730,6 +7150,20 @@
           <t>43</t>
         </is>
       </c>
+      <c r="K104" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>44.2</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
@@ -5782,6 +7216,20 @@
           <t>7</t>
         </is>
       </c>
+      <c r="K105" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
@@ -5834,6 +7282,20 @@
           <t>14</t>
         </is>
       </c>
+      <c r="K106" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>92.9</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
@@ -5886,6 +7348,20 @@
           <t>18</t>
         </is>
       </c>
+      <c r="K107" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
@@ -5938,6 +7414,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
@@ -5990,6 +7480,20 @@
           <t>24</t>
         </is>
       </c>
+      <c r="K109" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="5" t="inlineStr">
@@ -6042,6 +7546,20 @@
           <t>29</t>
         </is>
       </c>
+      <c r="K110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
@@ -6094,6 +7612,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="5" t="inlineStr">
@@ -6146,6 +7678,20 @@
           <t>21</t>
         </is>
       </c>
+      <c r="K112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
@@ -6198,6 +7744,20 @@
           <t>26</t>
         </is>
       </c>
+      <c r="K113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="48" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
@@ -6250,6 +7810,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K114" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="48" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
@@ -6302,6 +7876,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
@@ -6354,6 +7942,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
@@ -6406,6 +8008,20 @@
           <t>30</t>
         </is>
       </c>
+      <c r="K117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="5" t="inlineStr">
@@ -6458,6 +8074,20 @@
           <t>24</t>
         </is>
       </c>
+      <c r="K118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>43.5</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
@@ -6510,6 +8140,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="24" customHeight="1">
       <c r="A120" s="5" t="inlineStr">
@@ -6562,6 +8206,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
@@ -6614,6 +8272,20 @@
           <t>16</t>
         </is>
       </c>
+      <c r="K121" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="5" t="inlineStr">
@@ -6666,6 +8338,20 @@
           <t>28</t>
         </is>
       </c>
+      <c r="K122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="48" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
@@ -6718,6 +8404,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K123" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
@@ -6770,6 +8470,20 @@
           <t>14</t>
         </is>
       </c>
+      <c r="K124" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="24" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
@@ -6822,6 +8536,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K125" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
@@ -6874,6 +8602,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
@@ -6926,6 +8668,20 @@
           <t>12</t>
         </is>
       </c>
+      <c r="K127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>53.8</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="24" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
@@ -6978,6 +8734,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="24" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
@@ -7030,6 +8800,20 @@
           <t>12</t>
         </is>
       </c>
+      <c r="K129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="24" customHeight="1">
       <c r="A130" s="5" t="inlineStr">
@@ -7082,6 +8866,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="24" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
@@ -7134,6 +8932,20 @@
           <t>32</t>
         </is>
       </c>
+      <c r="K131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="24" customHeight="1">
       <c r="A132" s="5" t="inlineStr">
@@ -7186,6 +8998,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K132" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="24" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
@@ -7238,6 +9064,20 @@
           <t>13</t>
         </is>
       </c>
+      <c r="K133" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="24" customHeight="1">
       <c r="A134" s="5" t="inlineStr">
@@ -7290,6 +9130,20 @@
           <t>22</t>
         </is>
       </c>
+      <c r="K134" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>72.2</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="24" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
@@ -7342,6 +9196,20 @@
           <t>38</t>
         </is>
       </c>
+      <c r="K135" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="48" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
@@ -7394,6 +9262,20 @@
           <t>4</t>
         </is>
       </c>
+      <c r="K136" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>43.7</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="24" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
@@ -7446,6 +9328,20 @@
           <t>19</t>
         </is>
       </c>
+      <c r="K137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="24" customHeight="1">
       <c r="A138" s="5" t="inlineStr">
@@ -7498,6 +9394,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K138" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="24" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
@@ -7550,6 +9460,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="24" customHeight="1">
       <c r="A140" s="5" t="inlineStr">
@@ -7602,6 +9526,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="24" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
@@ -7654,6 +9592,20 @@
           <t>47</t>
         </is>
       </c>
+      <c r="K141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="24" customHeight="1">
       <c r="A142" s="5" t="inlineStr">
@@ -7706,6 +9658,20 @@
           <t>8</t>
         </is>
       </c>
+      <c r="K142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="24" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
@@ -7758,6 +9724,20 @@
           <t>21</t>
         </is>
       </c>
+      <c r="K143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="24" customHeight="1">
       <c r="A144" s="5" t="inlineStr">
@@ -7810,6 +9790,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K144" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="24" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
@@ -7862,6 +9856,20 @@
           <t>25</t>
         </is>
       </c>
+      <c r="K145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="24" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
@@ -7914,6 +9922,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="24" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
@@ -7966,6 +9988,20 @@
           <t>22</t>
         </is>
       </c>
+      <c r="K147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="24" customHeight="1">
       <c r="A148" s="5" t="inlineStr">
@@ -8018,6 +10054,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="24" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
@@ -8070,6 +10120,20 @@
           <t>41</t>
         </is>
       </c>
+      <c r="K149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>73.7</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="24" customHeight="1">
       <c r="A150" s="5" t="inlineStr">
@@ -8122,6 +10186,20 @@
           <t>15</t>
         </is>
       </c>
+      <c r="K150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="24" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
@@ -8174,6 +10252,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K151" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="24" customHeight="1">
       <c r="A152" s="5" t="inlineStr">
@@ -8226,6 +10318,20 @@
           <t>37</t>
         </is>
       </c>
+      <c r="K152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="24" customHeight="1">
       <c r="A153" s="7" t="inlineStr">
@@ -8278,6 +10384,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="24" customHeight="1">
       <c r="A154" s="5" t="inlineStr">
@@ -8330,6 +10450,20 @@
           <t>19</t>
         </is>
       </c>
+      <c r="K154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>61.1</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="24" customHeight="1">
       <c r="A155" s="7" t="inlineStr">
@@ -8382,6 +10516,20 @@
           <t>20</t>
         </is>
       </c>
+      <c r="K155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="24" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
@@ -8434,6 +10582,20 @@
           <t>51</t>
         </is>
       </c>
+      <c r="K156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>69.4</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="24" customHeight="1">
       <c r="A157" s="7" t="inlineStr">
@@ -8486,6 +10648,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K157" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="32" customHeight="1">
       <c r="A158" s="5" t="inlineStr">
@@ -8538,6 +10714,20 @@
           <t>8</t>
         </is>
       </c>
+      <c r="K158" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>42.9</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="24" customHeight="1">
       <c r="A159" s="7" t="inlineStr">
@@ -8588,6 +10778,20 @@
       <c r="J159" s="8" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="K159" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>2.7</t>
         </is>
       </c>
     </row>
@@ -8630,6 +10834,20 @@
       <c r="H160" s="6" t="inlineStr"/>
       <c r="I160" s="6" t="inlineStr"/>
       <c r="J160" s="6" t="inlineStr"/>
+      <c r="K160" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="24" customHeight="1">
       <c r="A161" s="7" t="inlineStr">
@@ -8682,6 +10900,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K161" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="24" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
@@ -8734,6 +10966,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K162" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="24" customHeight="1">
       <c r="A163" s="7" t="inlineStr">
@@ -8786,6 +11032,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K163" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="24" customHeight="1">
       <c r="A164" s="5" t="inlineStr">
@@ -8838,6 +11098,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K164" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="24" customHeight="1">
       <c r="A165" s="7" t="inlineStr">
@@ -8890,6 +11164,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K165" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="24" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
@@ -8942,6 +11230,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K166" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="24" customHeight="1">
       <c r="A167" s="7" t="inlineStr">
@@ -8994,6 +11296,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K167" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="24" customHeight="1">
       <c r="A168" s="5" t="inlineStr">
@@ -9046,6 +11362,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K168" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="24" customHeight="1">
       <c r="A169" s="7" t="inlineStr">
@@ -9098,6 +11428,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K169" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="24" customHeight="1">
       <c r="A170" s="5" t="inlineStr">
@@ -9150,6 +11494,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K170" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>2.9</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="24" customHeight="1">
       <c r="A171" s="7" t="inlineStr">
@@ -9202,6 +11560,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K171" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="24" customHeight="1">
       <c r="A172" s="5" t="inlineStr">
@@ -9254,6 +11626,20 @@
           <t>19</t>
         </is>
       </c>
+      <c r="K172" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="24" customHeight="1">
       <c r="A173" s="7" t="inlineStr">
@@ -9306,6 +11692,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K173" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="24" customHeight="1">
       <c r="A174" s="5" t="inlineStr">
@@ -9358,6 +11758,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K174" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="24" customHeight="1">
       <c r="A175" s="7" t="inlineStr">
@@ -9410,6 +11824,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K175" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="24" customHeight="1">
       <c r="A176" s="5" t="inlineStr">
@@ -9462,6 +11890,20 @@
           <t>6</t>
         </is>
       </c>
+      <c r="K176" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="24" customHeight="1">
       <c r="A177" s="7" t="inlineStr">
@@ -9514,6 +11956,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K177" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>94.7</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="24" customHeight="1">
       <c r="A178" s="5" t="inlineStr">
@@ -9566,6 +12022,20 @@
           <t>10</t>
         </is>
       </c>
+      <c r="K178" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="24" customHeight="1">
       <c r="A179" s="7" t="inlineStr">
@@ -9618,6 +12088,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K179" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="24" customHeight="1">
       <c r="A180" s="5" t="inlineStr">
@@ -9670,6 +12154,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K180" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>84.2</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="24" customHeight="1">
       <c r="A181" s="7" t="inlineStr">
@@ -9722,6 +12220,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K181" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="24" customHeight="1">
       <c r="A182" s="5" t="inlineStr">
@@ -9774,6 +12286,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K182" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="24" customHeight="1">
       <c r="A183" s="7" t="inlineStr">
@@ -9826,6 +12352,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K183" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="24" customHeight="1">
       <c r="A184" s="5" t="inlineStr">
@@ -9878,6 +12418,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K184" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="24" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
@@ -9930,6 +12484,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K185" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="24" customHeight="1">
       <c r="A186" s="5" t="inlineStr">
@@ -9982,6 +12550,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K186" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="24" customHeight="1">
       <c r="A187" s="7" t="inlineStr">
@@ -10034,6 +12616,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K187" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="24" customHeight="1">
       <c r="A188" s="5" t="inlineStr">
@@ -10086,6 +12682,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K188" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="24" customHeight="1">
       <c r="A189" s="7" t="inlineStr">
@@ -10138,6 +12748,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K189" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="24" customHeight="1">
       <c r="A190" s="5" t="inlineStr">
@@ -10190,6 +12814,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K190" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="24" customHeight="1">
       <c r="A191" s="7" t="inlineStr">
@@ -10242,6 +12880,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K191" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="24" customHeight="1">
       <c r="A192" s="5" t="inlineStr">
@@ -10294,6 +12946,20 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K192" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>43.6</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="24" customHeight="1">
       <c r="A193" s="7" t="inlineStr">
@@ -10346,6 +13012,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K193" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="24" customHeight="1">
       <c r="A194" s="5" t="inlineStr">
@@ -10398,6 +13078,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K194" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="24" customHeight="1">
       <c r="A195" s="7" t="inlineStr">
@@ -10450,6 +13144,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K195" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="24" customHeight="1">
       <c r="A196" s="5" t="inlineStr">
@@ -10502,6 +13210,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K196" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="24" customHeight="1">
       <c r="A197" s="7" t="inlineStr">
@@ -10554,6 +13276,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K197" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="24" customHeight="1">
       <c r="A198" s="5" t="inlineStr">
@@ -10606,6 +13342,20 @@
           <t>3</t>
         </is>
       </c>
+      <c r="K198" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="24" customHeight="1">
       <c r="A199" s="7" t="inlineStr">
@@ -10658,6 +13408,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K199" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="24" customHeight="1">
       <c r="A200" s="5" t="inlineStr">
@@ -10710,6 +13474,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K200" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="24" customHeight="1">
       <c r="A201" s="7" t="inlineStr">
@@ -10762,6 +13540,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K201" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="24" customHeight="1">
       <c r="A202" s="5" t="inlineStr">
@@ -10814,6 +13606,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K202" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="24" customHeight="1">
       <c r="A203" s="7" t="inlineStr">
@@ -10866,6 +13672,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K203" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="24" customHeight="1">
       <c r="A204" s="5" t="inlineStr">
@@ -10918,6 +13738,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K204" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="24" customHeight="1">
       <c r="A205" s="7" t="inlineStr">
@@ -10970,6 +13804,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K205" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="24" customHeight="1">
       <c r="A206" s="5" t="inlineStr">
@@ -11022,6 +13870,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K206" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="24" customHeight="1">
       <c r="A207" s="7" t="inlineStr">
@@ -11074,6 +13936,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K207" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>54.5</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="24" customHeight="1">
       <c r="A208" s="5" t="inlineStr">
@@ -11126,6 +14002,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K208" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>92.3</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="24" customHeight="1">
       <c r="A209" s="7" t="inlineStr">
@@ -11178,6 +14068,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K209" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="24" customHeight="1">
       <c r="A210" s="5" t="inlineStr">
@@ -11230,6 +14134,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K210" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="24" customHeight="1">
       <c r="A211" s="7" t="inlineStr">
@@ -11282,6 +14200,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K211" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="24" customHeight="1">
       <c r="A212" s="5" t="inlineStr">
@@ -11334,6 +14266,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K212" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="24" customHeight="1">
       <c r="A213" s="7" t="inlineStr">
@@ -11386,6 +14332,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K213" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="24" customHeight="1">
       <c r="A214" s="5" t="inlineStr">
@@ -11438,6 +14398,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K214" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="24" customHeight="1">
       <c r="A215" s="7" t="inlineStr">
@@ -11490,6 +14464,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K215" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="24" customHeight="1">
       <c r="A216" s="5" t="inlineStr">
@@ -11542,6 +14530,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K216" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="24" customHeight="1">
       <c r="A217" s="7" t="inlineStr">
@@ -11594,6 +14596,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K217" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="24" customHeight="1">
       <c r="A218" s="5" t="inlineStr">
@@ -11646,6 +14662,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K218" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="24" customHeight="1">
       <c r="A219" s="7" t="inlineStr">
@@ -11698,6 +14728,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K219" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="24" customHeight="1">
       <c r="A220" s="5" t="inlineStr">
@@ -11750,6 +14794,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K220" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="24" customHeight="1">
       <c r="A221" s="7" t="inlineStr">
@@ -11802,6 +14860,20 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K221" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="24" customHeight="1">
       <c r="A222" s="5" t="inlineStr">
@@ -11854,6 +14926,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K222" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="24" customHeight="1">
       <c r="A223" s="7" t="inlineStr">
@@ -11906,6 +14992,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K223" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="32" customHeight="1">
       <c r="A224" s="5" t="inlineStr">
@@ -11956,6 +15056,20 @@
       <c r="J224" s="6" t="inlineStr">
         <is>
           <t>10</t>
+        </is>
+      </c>
+      <c r="K224" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>3.4</t>
         </is>
       </c>
     </row>
@@ -12050,6 +15164,20 @@
       <c r="H226" s="6" t="inlineStr"/>
       <c r="I226" s="6" t="inlineStr"/>
       <c r="J226" s="6" t="inlineStr"/>
+      <c r="K226" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="32" customHeight="1">
       <c r="A227" s="7" t="inlineStr">
@@ -12610,6 +15738,20 @@
       <c r="H240" s="6" t="inlineStr"/>
       <c r="I240" s="6" t="inlineStr"/>
       <c r="J240" s="6" t="inlineStr"/>
+      <c r="K240" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="32" customHeight="1">
       <c r="A241" s="7" t="inlineStr">
@@ -12650,6 +15792,20 @@
       <c r="H241" s="8" t="inlineStr"/>
       <c r="I241" s="8" t="inlineStr"/>
       <c r="J241" s="8" t="inlineStr"/>
+      <c r="K241" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="32" customHeight="1">
       <c r="A242" s="5" t="inlineStr">
@@ -12850,6 +16006,20 @@
       <c r="H246" s="6" t="inlineStr"/>
       <c r="I246" s="6" t="inlineStr"/>
       <c r="J246" s="6" t="inlineStr"/>
+      <c r="K246" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="32" customHeight="1">
       <c r="A247" s="7" t="inlineStr">
@@ -12970,6 +16140,20 @@
       <c r="H249" s="8" t="inlineStr"/>
       <c r="I249" s="8" t="inlineStr"/>
       <c r="J249" s="8" t="inlineStr"/>
+      <c r="K249" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="32" customHeight="1">
       <c r="A250" s="5" t="inlineStr">
@@ -13010,6 +16194,20 @@
       <c r="H250" s="6" t="inlineStr"/>
       <c r="I250" s="6" t="inlineStr"/>
       <c r="J250" s="6" t="inlineStr"/>
+      <c r="K250" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="32" customHeight="1">
       <c r="A251" s="7" t="inlineStr">
@@ -13290,6 +16488,20 @@
       <c r="H257" s="8" t="inlineStr"/>
       <c r="I257" s="8" t="inlineStr"/>
       <c r="J257" s="8" t="inlineStr"/>
+      <c r="K257" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="32" customHeight="1">
       <c r="A258" s="5" t="inlineStr">
@@ -13490,6 +16702,20 @@
       <c r="H262" s="6" t="inlineStr"/>
       <c r="I262" s="6" t="inlineStr"/>
       <c r="J262" s="6" t="inlineStr"/>
+      <c r="K262" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="32" customHeight="1">
       <c r="A263" s="7" t="inlineStr">
@@ -13610,6 +16836,20 @@
       <c r="H265" s="8" t="inlineStr"/>
       <c r="I265" s="8" t="inlineStr"/>
       <c r="J265" s="8" t="inlineStr"/>
+      <c r="K265" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="32" customHeight="1">
       <c r="A266" s="5" t="inlineStr">
@@ -13650,6 +16890,20 @@
       <c r="H266" s="6" t="inlineStr"/>
       <c r="I266" s="6" t="inlineStr"/>
       <c r="J266" s="6" t="inlineStr"/>
+      <c r="K266" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="32" customHeight="1">
       <c r="A267" s="7" t="inlineStr">
@@ -13730,6 +16984,20 @@
       <c r="H268" s="6" t="inlineStr"/>
       <c r="I268" s="6" t="inlineStr"/>
       <c r="J268" s="6" t="inlineStr"/>
+      <c r="K268" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="32" customHeight="1">
       <c r="A269" s="7" t="inlineStr">
@@ -13810,6 +17078,20 @@
       <c r="H270" s="6" t="inlineStr"/>
       <c r="I270" s="6" t="inlineStr"/>
       <c r="J270" s="6" t="inlineStr"/>
+      <c r="K270" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="32" customHeight="1">
       <c r="A271" s="7" t="inlineStr">
@@ -14050,6 +17332,20 @@
       <c r="H276" s="6" t="inlineStr"/>
       <c r="I276" s="6" t="inlineStr"/>
       <c r="J276" s="6" t="inlineStr"/>
+      <c r="K276" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="32" customHeight="1">
       <c r="A277" s="7" t="inlineStr">
@@ -14450,6 +17746,20 @@
       <c r="H286" s="6" t="inlineStr"/>
       <c r="I286" s="6" t="inlineStr"/>
       <c r="J286" s="6" t="inlineStr"/>
+      <c r="K286" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="32" customHeight="1">
       <c r="A287" s="7" t="inlineStr">
@@ -14490,6 +17800,20 @@
       <c r="H287" s="8" t="inlineStr"/>
       <c r="I287" s="8" t="inlineStr"/>
       <c r="J287" s="8" t="inlineStr"/>
+      <c r="K287" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="32" customHeight="1">
       <c r="A288" s="5" t="inlineStr">
@@ -14530,6 +17854,20 @@
       <c r="H288" s="6" t="inlineStr"/>
       <c r="I288" s="6" t="inlineStr"/>
       <c r="J288" s="6" t="inlineStr"/>
+      <c r="K288" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="32" customHeight="1">
       <c r="A289" s="7" t="inlineStr">
@@ -14890,6 +18228,20 @@
       <c r="H297" s="8" t="inlineStr"/>
       <c r="I297" s="8" t="inlineStr"/>
       <c r="J297" s="8" t="inlineStr"/>
+      <c r="K297" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="32" customHeight="1">
       <c r="A298" s="5" t="inlineStr">
@@ -15090,6 +18442,20 @@
       <c r="H302" s="6" t="inlineStr"/>
       <c r="I302" s="6" t="inlineStr"/>
       <c r="J302" s="6" t="inlineStr"/>
+      <c r="K302" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="32" customHeight="1">
       <c r="A303" s="7" t="inlineStr">
@@ -15210,6 +18576,12 @@
       <c r="H305" s="8" t="inlineStr"/>
       <c r="I305" s="8" t="inlineStr"/>
       <c r="J305" s="8" t="inlineStr"/>
+      <c r="K305" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
     </row>
     <row r="306" ht="32" customHeight="1">
       <c r="A306" s="5" t="inlineStr">
@@ -15850,6 +19222,20 @@
       <c r="H321" s="8" t="inlineStr"/>
       <c r="I321" s="8" t="inlineStr"/>
       <c r="J321" s="8" t="inlineStr"/>
+      <c r="K321" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="32" customHeight="1">
       <c r="A322" s="5" t="inlineStr">
@@ -16010,6 +19396,20 @@
       <c r="H325" s="8" t="inlineStr"/>
       <c r="I325" s="8" t="inlineStr"/>
       <c r="J325" s="8" t="inlineStr"/>
+      <c r="K325" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="326" ht="32" customHeight="1">
       <c r="A326" s="5" t="inlineStr">
@@ -16090,6 +19490,20 @@
       <c r="H327" s="8" t="inlineStr"/>
       <c r="I327" s="8" t="inlineStr"/>
       <c r="J327" s="8" t="inlineStr"/>
+      <c r="K327" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
     </row>
     <row r="328" ht="32" customHeight="1">
       <c r="A328" s="5" t="inlineStr">
@@ -16210,6 +19624,20 @@
       <c r="H330" s="6" t="inlineStr"/>
       <c r="I330" s="6" t="inlineStr"/>
       <c r="J330" s="6" t="inlineStr"/>
+      <c r="K330" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="331" ht="32" customHeight="1">
       <c r="A331" s="7" t="inlineStr">
@@ -16290,6 +19718,20 @@
       <c r="H332" s="6" t="inlineStr"/>
       <c r="I332" s="6" t="inlineStr"/>
       <c r="J332" s="6" t="inlineStr"/>
+      <c r="K332" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
     </row>
     <row r="333" ht="32" customHeight="1">
       <c r="A333" s="7" t="inlineStr">
@@ -16730,6 +20172,20 @@
       <c r="H343" s="8" t="inlineStr"/>
       <c r="I343" s="8" t="inlineStr"/>
       <c r="J343" s="8" t="inlineStr"/>
+      <c r="K343" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
     </row>
     <row r="344" ht="32" customHeight="1">
       <c r="A344" s="5" t="inlineStr">
@@ -16810,6 +20266,20 @@
       <c r="H345" s="8" t="inlineStr"/>
       <c r="I345" s="8" t="inlineStr"/>
       <c r="J345" s="8" t="inlineStr"/>
+      <c r="K345" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M345" t="inlineStr"/>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="346" ht="32" customHeight="1">
       <c r="A346" s="5" t="inlineStr">
@@ -16890,6 +20360,20 @@
       <c r="H347" s="8" t="inlineStr"/>
       <c r="I347" s="8" t="inlineStr"/>
       <c r="J347" s="8" t="inlineStr"/>
+      <c r="K347" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
     </row>
     <row r="348" ht="32" customHeight="1">
       <c r="A348" s="5" t="inlineStr">
@@ -17130,6 +20614,20 @@
       <c r="H353" s="8" t="inlineStr"/>
       <c r="I353" s="8" t="inlineStr"/>
       <c r="J353" s="8" t="inlineStr"/>
+      <c r="K353" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
     </row>
     <row r="354" ht="48" customHeight="1">
       <c r="A354" s="5" t="inlineStr">
@@ -17170,6 +20668,20 @@
       <c r="H354" s="6" t="inlineStr"/>
       <c r="I354" s="6" t="inlineStr"/>
       <c r="J354" s="6" t="inlineStr"/>
+      <c r="K354" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr"/>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
     </row>
     <row r="355" ht="48" customHeight="1">
       <c r="A355" s="7" t="inlineStr">
@@ -17210,6 +20722,20 @@
       <c r="H355" s="8" t="inlineStr"/>
       <c r="I355" s="8" t="inlineStr"/>
       <c r="J355" s="8" t="inlineStr"/>
+      <c r="K355" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
     </row>
     <row r="356" ht="48" customHeight="1">
       <c r="A356" s="5" t="inlineStr">
@@ -17250,6 +20776,20 @@
       <c r="H356" s="6" t="inlineStr"/>
       <c r="I356" s="6" t="inlineStr"/>
       <c r="J356" s="6" t="inlineStr"/>
+      <c r="K356" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:J356"/>
